--- a/reports/二级子公司D_利润表_2026-12.xlsx
+++ b/reports/二级子公司D_利润表_2026-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>83310853</v>
+        <v>85154182</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>81472720</v>
+        <v>81535106</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1029479362</v>
+        <v>1029715598</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>280631</v>
+        <v>278891</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3490522</v>
+        <v>3492598</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>240863</v>
+        <v>238607</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2990561</v>
+        <v>2992755</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>198887</v>
+        <v>198643</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2492126</v>
+        <v>2492973</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>179310</v>
+        <v>178788</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2243902</v>
+        <v>2242725</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>100475</v>
+        <v>99435</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1246430</v>
+        <v>1245489</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>80011</v>
+        <v>79701</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>996755</v>
+        <v>996132</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>82230676</v>
+        <v>84080117</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>80392543</v>
+        <v>80461041</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4521444</v>
+        <v>4514834</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>56078547</v>
+        <v>56044663</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>348676</v>
+        <v>351639</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4360916</v>
+        <v>4360614</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>596642</v>
+        <v>603052</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>7479113</v>
+        <v>7478485</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>72256385</v>
+        <v>72319508</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>914820422</v>
+        <v>915047325</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1202758</v>
+        <v>1203419</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>14951962</v>
+        <v>14967774</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>397426</v>
+        <v>400240</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4984605</v>
+        <v>4990126</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1995522</v>
+        <v>1996176</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>24933062</v>
+        <v>24950645</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>502543</v>
+        <v>497877</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6231651</v>
+        <v>6236580</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1797171</v>
+        <v>1789214</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>22426862</v>
+        <v>22444573</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40962</v>
+        <v>40955</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>494438</v>
+        <v>494444</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1072823</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>13455628</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>716084</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8967156</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>54744580</v>
+        <v>58476338</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>49117065</v>
+        <v>48974437</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>48216398</v>
+        <v>48071259</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>598303605</v>
+        <v>597679381</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>900667</v>
+        <v>903178</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>11213570</v>
+        <v>11209411</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1808635</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>22427227</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>578915</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>7179751</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>361539</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4489125</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>433115</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5388574</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>324088</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4042045</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>215516</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2694633</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>179186</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2245089</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>844758</v>
+        <v>844762</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10591998</v>
+        <v>10598294</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>648155</v>
+        <v>645530</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>8103171</v>
+        <v>8101245</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>502509</v>
+        <v>496730</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6231839</v>
+        <v>6229126</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3796390</v>
+        <v>3780199</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>47345548</v>
+        <v>47324753</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>153588</v>
+        <v>149532</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1854072</v>
+        <v>1867669</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>330270</v>
+        <v>329684</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3956565</v>
+        <v>3950732</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>372737</v>
+        <v>329684</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4448912</v>
+        <v>3950732</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41044</v>
+        <v>41392</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>494257</v>
+        <v>494071</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>167827</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2001856</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>316580</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3926646</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111796</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1335787</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83697</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1002151</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>139167</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1670488</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>448844</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5613728</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>73872</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>890653</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55319</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>667730</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92144</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1112358</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64532</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>778290</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46161</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>555712</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>37009</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>444471</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27826</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>333344</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27486096</v>
+        <v>26721186</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31568952</v>
+        <v>29673120</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>180895</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2242972</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46621</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>556371</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>71863</v>
+        <v>72447</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>864931</v>
+        <v>865831</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27414233</v>
+        <v>26829634</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2587264</v>
+        <v>2576299</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>30907330</v>
+        <v>30935062</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24826969</v>
+        <v>24253335</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24826969</v>
+        <v>24253335</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24826969</v>
+        <v>24253335</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24826969</v>
+        <v>24253335</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24826969</v>
+        <v>24253335</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
